--- a/artfynd/A 70072-2021 artfynd.xlsx
+++ b/artfynd/A 70072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98382232</v>
+        <v>98382098</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hällsjön, södra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588993.8601447045</v>
+        <v>588993</v>
       </c>
       <c r="R2" t="n">
-        <v>6926930.485810703</v>
+        <v>6926864</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,12 +765,18 @@
           <t>12:40</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett flertal mindre rosentickor på tillväxt på en granlåga.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,51 +795,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98382319</v>
+        <v>98382529</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hällsjön, södra sidan. Vid bäck., Mpd</t>
+          <t>Hällsjön, södra sidan. Nära sjön., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589013.6558644846</v>
+        <v>589073</v>
       </c>
       <c r="R3" t="n">
-        <v>6926935.643675778</v>
+        <v>6927096</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -883,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98382529</v>
+        <v>98382232</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,37 +917,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hällsjön, södra sidan. Nära sjön., Mpd</t>
+          <t>Hällsjön, södra sidan., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589073.816385238</v>
+        <v>588994</v>
       </c>
       <c r="R4" t="n">
-        <v>6927095.560704201</v>
+        <v>6926930</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1014,6 +1011,114 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98382319</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hällsjön, södra sidan. Vid bäck., Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>589014</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6926935</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-01-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-01-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70072-2021 artfynd.xlsx
+++ b/artfynd/A 70072-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98382098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98382529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98382232</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,8 +1139,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98382319</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>